--- a/survey_templates/033_lymphedema_device_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/033_lymphedema_device_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -907,8 +907,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -936,12 +936,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'every_day'}</t>
+          <t>every_day</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Every day'}</t>
+          <t>Every day</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'almost_every_day'}</t>
+          <t>almost_every_day</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Almost every day'}</t>
+          <t>Almost every day</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'several_times_a_week'}</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Several times a week'}</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'no_issues'}</t>
+          <t>no_issues</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'No issues'}</t>
+          <t>No issues</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'minor_issues'}</t>
+          <t>minor_issues</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Minor issues'}</t>
+          <t>Minor issues</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'some_issues'}</t>
+          <t>some_issues</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Some issues'}</t>
+          <t>Some issues</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'serious_issues'}</t>
+          <t>serious_issues</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Serious issues'}</t>
+          <t>Serious issues</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'extremely_serious_issues'}</t>
+          <t>extremely_serious_issues</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Extremely serious issues'}</t>
+          <t>Extremely serious issues</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_comfortable'}</t>
+          <t>not_at_all_comfortable</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all comfortable'}</t>
+          <t>Not at all comfortable</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_comfortable'}</t>
+          <t>somewhat_comfortable</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat comfortable'}</t>
+          <t>Somewhat comfortable</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_uncomfortable'}</t>
+          <t>somewhat_uncomfortable</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat uncomfortable'}</t>
+          <t>Somewhat uncomfortable</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'very_uncomfortable'}</t>
+          <t>very_uncomfortable</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Very uncomfortable'}</t>
+          <t>Very uncomfortable</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'category_1'}</t>
+          <t>category_1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Category 1'}</t>
+          <t>Category 1</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'category_2'}</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Category 2'}</t>
+          <t>Category 2</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'category_3'}</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Category 3'}</t>
+          <t>Category 3</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'category_4'}</t>
+          <t>category_4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Category 4'}</t>
+          <t>Category 4</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'category_5'}</t>
+          <t>category_5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Category 5'}</t>
+          <t>Category 5</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'tag_1'}</t>
+          <t>tag_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 1'}</t>
+          <t>Tag 1</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'tag_2'}</t>
+          <t>tag_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 2'}</t>
+          <t>Tag 2</t>
         </is>
       </c>
     </row>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'tag_3'}</t>
+          <t>tag_3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 3'}</t>
+          <t>Tag 3</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'tag_4'}</t>
+          <t>tag_4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 4'}</t>
+          <t>Tag 4</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'tag_5'}</t>
+          <t>tag_5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 5'}</t>
+          <t>Tag 5</t>
         </is>
       </c>
     </row>
